--- a/data/faillissementen_sbi49_data.xlsx
+++ b/data/faillissementen_sbi49_data.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site per jaar" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faillissementen'!$A$1:$P$867</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Faillissementen'!$A$1:$Q$867</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CBS maand'!$A$1:$D$213</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Dieselprijs'!$A$1:$B$249</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Top 30 plaatsen'!$A$1:$B$31</definedName>
@@ -38,7 +38,7 @@
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,10 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -97,7 +101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -113,6 +117,8 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1008,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1174,7 +1180,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Curatornamen en plaatsnamen zijn hersteld van tekencodering. Enkele vroege records hebben in de bron afgekapte bedrijfsnamen.</t>
+          <t>Curatornamen en plaatsnamen zijn hersteld van tekencodering (mojibake). Zie de aparte regel over afgekapte bedrijfsnamen hieronder.</t>
         </is>
       </c>
     </row>
@@ -1187,6 +1193,30 @@
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Faillissementen - Site vs CBS - CBS jaar - CBS maand - Dieselprijs - Dieselprijs jaar - Provincies - Top 30 plaatsen - Rechtsvormen - Site per jaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Let op: afgekapte namen</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Van de 866 records zijn er 111 met een afgekapte bedrijfsnaam - te herkennen aan kolom Q in het blad Faillissementen. Dit is een fout in de oorspronkelijke oogst: faillissementen.com beperkte de verzoeken, waardoor onvolledige paginawaarden zijn opgeslagen. Bewijs: de detailpagina van KvK 27196576 geeft "R Hoekstra (inter)nationaal Transport", terwijl hier "R Hoekstra (inter)nationa" staat. Een her-oogst loopt; de site geeft nu "Limit reached" terug. Gebruik het KvK-nummer als harde identifier, niet de naam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Let op: afgekapte activiteit</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Bij 499 records is de activiteitomschrijving afgekapt IN DE BRON zelf (bijv. "Goederenvervoer over weg (geen verhuiz.)."). Dit is niet te herstellen door opnieuw op te halen. De SBI-code is wel volledig.</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1276,7 @@
       <c r="C2" t="n">
         <v>597</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="11">
         <f>IFERROR(C2/SUM($C$2:$C$7),"")</f>
         <v/>
       </c>
@@ -1265,7 +1295,7 @@
       <c r="C3" t="n">
         <v>126</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="11">
         <f>IFERROR(C3/SUM($C$2:$C$7),"")</f>
         <v/>
       </c>
@@ -1284,7 +1314,7 @@
       <c r="C4" t="n">
         <v>120</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="11">
         <f>IFERROR(C4/SUM($C$2:$C$7),"")</f>
         <v/>
       </c>
@@ -1303,7 +1333,7 @@
       <c r="C5" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <f>IFERROR(C5/SUM($C$2:$C$7),"")</f>
         <v/>
       </c>
@@ -1322,7 +1352,7 @@
       <c r="C6" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="11">
         <f>IFERROR(C6/SUM($C$2:$C$7),"")</f>
         <v/>
       </c>
@@ -1341,7 +1371,7 @@
       <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <f>IFERROR(C7/SUM($C$2:$C$7),"")</f>
         <v/>
       </c>
@@ -1443,7 +1473,7 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>IFERROR(C2/B2,"")</f>
         <v/>
       </c>
@@ -1482,7 +1512,7 @@
       <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="11">
         <f>IFERROR(C3/B3,"")</f>
         <v/>
       </c>
@@ -1521,7 +1551,7 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="11">
         <f>IFERROR(C4/B4,"")</f>
         <v/>
       </c>
@@ -1560,7 +1590,7 @@
       <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="11">
         <f>IFERROR(C5/B5,"")</f>
         <v/>
       </c>
@@ -1599,7 +1629,7 @@
       <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="11">
         <f>IFERROR(C6/B6,"")</f>
         <v/>
       </c>
@@ -1638,7 +1668,7 @@
       <c r="D7" t="n">
         <v>12</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="11">
         <f>IFERROR(C7/B7,"")</f>
         <v/>
       </c>
@@ -1677,7 +1707,7 @@
       <c r="D8" t="n">
         <v>37</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="11">
         <f>IFERROR(C8/B8,"")</f>
         <v/>
       </c>
@@ -1716,7 +1746,7 @@
       <c r="D9" t="n">
         <v>58</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="11">
         <f>IFERROR(C9/B9,"")</f>
         <v/>
       </c>
@@ -1755,7 +1785,7 @@
       <c r="D10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="11">
         <f>IFERROR(C10/B10,"")</f>
         <v/>
       </c>
@@ -1794,7 +1824,7 @@
       <c r="D11" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="11">
         <f>IFERROR(C11/B11,"")</f>
         <v/>
       </c>
@@ -1833,7 +1863,7 @@
       <c r="D12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="11">
         <f>IFERROR(C12/B12,"")</f>
         <v/>
       </c>
@@ -1872,7 +1902,7 @@
       <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="11">
         <f>IFERROR(C13/B13,"")</f>
         <v/>
       </c>
@@ -1911,7 +1941,7 @@
       <c r="D14" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="11">
         <f>IFERROR(C14/B14,"")</f>
         <v/>
       </c>
@@ -1950,7 +1980,7 @@
       <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="11">
         <f>IFERROR(C15/B15,"")</f>
         <v/>
       </c>
@@ -1989,7 +2019,7 @@
       <c r="D16" t="n">
         <v>13</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="11">
         <f>IFERROR(C16/B16,"")</f>
         <v/>
       </c>
@@ -2028,7 +2058,7 @@
       <c r="D17" t="n">
         <v>35</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="11">
         <f>IFERROR(C17/B17,"")</f>
         <v/>
       </c>
@@ -2067,7 +2097,7 @@
       <c r="D18" t="n">
         <v>19</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="11">
         <f>IFERROR(C18/B18,"")</f>
         <v/>
       </c>
@@ -2106,7 +2136,7 @@
       <c r="D19" t="n">
         <v>15</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="11">
         <f>IFERROR(C19/B19,"")</f>
         <v/>
       </c>
@@ -2145,7 +2175,7 @@
       <c r="D20" t="n">
         <v>47</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="11">
         <f>IFERROR(C20/B20,"")</f>
         <v/>
       </c>
@@ -2184,7 +2214,7 @@
       <c r="D21" t="n">
         <v>68</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="11">
         <f>IFERROR(C21/B21,"")</f>
         <v/>
       </c>
@@ -2223,7 +2253,7 @@
       <c r="D22" t="n">
         <v>91</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="11">
         <f>IFERROR(C22/B22,"")</f>
         <v/>
       </c>
@@ -2262,7 +2292,7 @@
       <c r="D23" t="n">
         <v>140</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="11">
         <f>IFERROR(C23/B23,"")</f>
         <v/>
       </c>
@@ -2300,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P867"/>
+  <dimension ref="A1:Q867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2319,6 +2349,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2402,6 +2433,11 @@
           <t>Rechtsvorm (brontekst)</t>
         </is>
       </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>Naam afgekapt?</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2482,6 +2518,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2562,6 +2603,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2642,6 +2684,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2722,6 +2765,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2802,6 +2846,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2882,6 +2927,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2962,6 +3008,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3042,6 +3089,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3122,6 +3170,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3202,6 +3251,7 @@
           <t>Commanditaire vennootschap</t>
         </is>
       </c>
+      <c r="Q11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3282,6 +3332,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3362,6 +3413,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3442,6 +3498,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3522,6 +3579,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3602,6 +3660,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3682,6 +3741,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q17" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3762,6 +3826,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3842,6 +3907,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3922,6 +3988,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4002,6 +4069,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4082,6 +4150,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4162,6 +4231,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4242,6 +4312,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4322,6 +4393,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4402,6 +4474,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4482,6 +4555,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4562,6 +4636,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4642,6 +4717,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4722,6 +4798,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4802,6 +4883,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4882,6 +4964,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4962,6 +5045,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5042,6 +5126,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5122,6 +5207,7 @@
           <t>Commanditaire Vennootschap</t>
         </is>
       </c>
+      <c r="Q35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5202,6 +5288,7 @@
           <t>Commanditaire Vennootschap</t>
         </is>
       </c>
+      <c r="Q36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5282,6 +5369,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5362,6 +5450,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5442,6 +5531,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5522,6 +5612,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5602,6 +5693,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5682,6 +5774,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5762,6 +5855,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q43" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5842,6 +5940,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5922,6 +6021,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6002,6 +6102,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6082,6 +6183,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q47" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6162,6 +6268,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6242,6 +6349,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6322,6 +6430,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6402,6 +6511,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6482,6 +6592,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6562,6 +6673,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6642,6 +6754,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6722,6 +6835,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6802,6 +6916,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6882,6 +6997,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6962,6 +7078,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7042,6 +7159,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7122,6 +7240,7 @@
           <t>Commanditaire vennootschap</t>
         </is>
       </c>
+      <c r="Q60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7202,6 +7321,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q61" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7282,6 +7406,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7362,6 +7487,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7442,6 +7568,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q64" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7522,6 +7653,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7602,6 +7734,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7682,6 +7815,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7762,6 +7896,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7842,6 +7977,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7922,6 +8058,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8002,6 +8139,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8078,6 +8216,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q72" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8154,6 +8297,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8234,6 +8378,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8314,6 +8459,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8394,6 +8540,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8474,6 +8621,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8554,6 +8702,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8634,6 +8783,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8714,6 +8864,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8794,6 +8945,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8874,6 +9026,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8954,6 +9107,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9034,6 +9188,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9114,6 +9269,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9194,6 +9350,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9274,6 +9431,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9354,6 +9512,11 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q88" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9434,6 +9597,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9514,6 +9678,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9594,6 +9759,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9674,6 +9840,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q92" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9754,6 +9925,11 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q93" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9834,6 +10010,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9914,6 +10091,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9994,6 +10172,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10074,6 +10253,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q97" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10150,6 +10334,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10230,6 +10415,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10310,6 +10496,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10390,6 +10577,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10466,6 +10654,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10546,6 +10735,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10626,6 +10816,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q104" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10706,6 +10901,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10786,6 +10982,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10866,6 +11063,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10942,6 +11140,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11022,6 +11221,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11102,6 +11302,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11182,6 +11383,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11262,6 +11464,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11338,6 +11541,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11418,6 +11622,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11498,6 +11703,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11578,6 +11784,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11658,6 +11865,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11738,6 +11946,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11818,6 +12027,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11898,6 +12108,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q120" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11978,6 +12193,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12058,6 +12274,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12138,6 +12355,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q123" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12214,6 +12436,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12294,6 +12517,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12374,6 +12598,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12450,6 +12675,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q127" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12530,6 +12760,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12610,6 +12841,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12690,6 +12922,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12770,6 +13003,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12846,6 +13080,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12926,6 +13161,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q133" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13006,6 +13246,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13086,6 +13327,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q135" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13166,6 +13412,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q136" s="10" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13246,6 +13493,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q137" s="10" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13326,6 +13574,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q138" s="10" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13406,6 +13655,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q139" s="10" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13486,6 +13736,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q140" s="10" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13562,6 +13813,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q141" s="10" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13642,6 +13894,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q142" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13722,6 +13979,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q143" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13802,6 +14064,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q144" s="10" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13882,6 +14145,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q145" s="10" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13962,6 +14226,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q146" s="10" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14042,6 +14307,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q147" s="10" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14122,6 +14388,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q148" s="10" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14202,6 +14469,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q149" s="10" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14282,6 +14550,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q150" s="10" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14362,6 +14631,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q151" s="10" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14442,6 +14712,7 @@
           <t>Buitenlandse rechtsvorm</t>
         </is>
       </c>
+      <c r="Q152" s="10" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14522,6 +14793,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q153" s="10" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14598,6 +14870,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q154" s="10" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14678,6 +14951,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q155" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14758,6 +15036,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q156" s="10" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14838,6 +15117,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q157" s="10" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14918,6 +15198,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q158" s="10" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14998,6 +15279,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q159" s="10" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15078,6 +15360,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q160" s="10" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15158,6 +15441,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q161" s="10" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15238,6 +15522,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q162" s="10" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15318,6 +15603,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q163" s="10" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15398,6 +15684,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q164" s="10" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15478,6 +15765,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q165" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15558,6 +15850,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q166" s="10" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15638,6 +15931,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q167" s="10" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15718,6 +16012,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q168" s="10" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15798,6 +16093,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q169" s="10" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15878,6 +16174,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q170" s="10" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -15958,6 +16255,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q171" s="10" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16038,6 +16336,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q172" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16118,6 +16421,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q173" s="10" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16198,6 +16502,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q174" s="10" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16278,6 +16583,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q175" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16358,6 +16668,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q176" s="10" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16438,6 +16749,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q177" s="10" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16514,6 +16826,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q178" s="10" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16594,6 +16907,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q179" s="10" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16674,6 +16988,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q180" s="10" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -16746,6 +17061,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q181" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -16826,6 +17146,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q182" s="10" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16906,6 +17227,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q183" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16986,6 +17312,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q184" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17066,6 +17397,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q185" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17146,6 +17482,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q186" s="10" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -17226,6 +17563,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q187" s="10" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17306,6 +17644,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q188" s="10" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17386,6 +17725,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -17466,6 +17806,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q190" s="10" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -17546,6 +17887,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q191" s="10" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -17626,6 +17968,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q192" s="10" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -17706,6 +18049,11 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q193" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -17786,6 +18134,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q194" s="10" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -17866,6 +18215,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q195" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -17946,6 +18300,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q196" s="10" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -18026,6 +18381,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q197" s="10" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -18106,6 +18462,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q198" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18186,6 +18547,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q199" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -18266,6 +18632,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q200" s="10" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18346,6 +18713,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q201" s="10" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18426,6 +18794,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q202" s="10" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -18506,6 +18875,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q203" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -18586,6 +18960,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q204" s="10" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -18666,6 +19041,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q205" s="10" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -18746,6 +19122,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q206" s="10" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -18826,6 +19203,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q207" s="10" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -18906,6 +19284,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q208" s="10" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -18986,6 +19365,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q209" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -19066,6 +19450,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q210" s="10" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -19146,6 +19531,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q211" s="10" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -19226,6 +19612,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q212" s="10" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -19302,6 +19689,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q213" s="10" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -19378,6 +19766,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q214" s="10" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -19458,6 +19847,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q215" s="10" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -19538,6 +19928,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q216" s="10" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -19618,6 +20009,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q217" s="10" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -19698,6 +20090,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q218" s="10" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -19778,6 +20171,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q219" s="10" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19858,6 +20252,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q220" s="10" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -19938,6 +20333,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q221" s="10" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -20018,6 +20414,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q222" s="10" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -20098,6 +20495,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q223" s="10" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -20178,6 +20576,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q224" s="10" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -20258,6 +20657,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q225" s="10" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -20338,6 +20738,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q226" s="10" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -20418,6 +20819,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q227" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -20498,6 +20904,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q228" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -20578,6 +20989,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q229" s="10" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -20658,6 +21070,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q230" s="10" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -20738,6 +21151,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q231" s="10" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -20818,6 +21232,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q232" s="10" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -20898,6 +21313,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q233" s="10" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -20978,6 +21394,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q234" s="10" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -21058,6 +21475,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q235" s="10" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -21138,6 +21556,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q236" s="10" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -21218,6 +21637,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q237" s="10" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -21298,6 +21718,11 @@
           <t>Commanditaire Vennootschap</t>
         </is>
       </c>
+      <c r="Q238" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -21378,6 +21803,11 @@
           <t>Commanditaire Vennootschap</t>
         </is>
       </c>
+      <c r="Q239" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -21458,6 +21888,11 @@
           <t>Commanditaire Vennootschap</t>
         </is>
       </c>
+      <c r="Q240" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -21538,6 +21973,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q241" s="10" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -21618,6 +22054,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q242" s="10" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -21698,6 +22135,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q243" s="10" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -21778,6 +22216,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q244" s="10" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -21858,6 +22297,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q245" s="10" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -21938,6 +22378,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q246" s="10" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -22010,6 +22451,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q247" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -22090,6 +22536,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q248" s="10" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -22170,6 +22617,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q249" s="10" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -22250,6 +22698,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q250" s="10" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -22330,6 +22779,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q251" s="10" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -22410,6 +22860,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q252" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -22490,6 +22945,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q253" s="10" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -22570,6 +23026,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q254" s="10" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -22650,6 +23107,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q255" s="10" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -22730,6 +23188,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q256" s="10" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -22810,6 +23269,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q257" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -22890,6 +23354,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q258" s="10" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -22970,6 +23435,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q259" s="10" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -23046,6 +23512,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q260" s="10" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -23122,6 +23589,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q261" s="10" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -23202,6 +23670,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q262" s="10" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -23282,6 +23751,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q263" s="10" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -23362,6 +23832,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q264" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -23442,6 +23917,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q265" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -23522,6 +24002,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q266" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -23602,6 +24087,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q267" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -23682,6 +24172,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q268" s="10" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -23762,6 +24253,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q269" s="10" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -23842,6 +24334,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q270" s="10" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -23922,6 +24415,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q271" s="10" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -24002,6 +24496,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q272" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -24082,6 +24581,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q273" s="10" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -24162,6 +24662,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q274" s="10" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -24242,6 +24743,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q275" s="10" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -24322,6 +24824,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q276" s="10" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -24402,6 +24905,11 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q277" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -24482,6 +24990,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q278" s="10" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -24562,6 +25071,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q279" s="10" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -24642,6 +25152,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q280" s="10" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -24722,6 +25233,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q281" s="10" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -24802,6 +25314,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q282" s="10" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -24882,6 +25395,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q283" s="10" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -24962,6 +25476,7 @@
           <t>eenmanszaak</t>
         </is>
       </c>
+      <c r="Q284" s="10" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -25042,6 +25557,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q285" s="10" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -25122,6 +25638,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q286" s="10" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -25202,6 +25719,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q287" s="10" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -25282,6 +25800,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q288" s="10" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -25362,6 +25881,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q289" s="10" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -25442,6 +25962,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q290" s="10" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -25518,6 +26039,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q291" s="10" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -25598,6 +26120,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q292" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -25678,6 +26205,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q293" s="10" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -25758,6 +26286,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q294" s="10" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -25838,6 +26367,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q295" s="10" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -25918,6 +26448,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q296" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -25998,6 +26533,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q297" s="10" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -26078,6 +26614,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q298" s="10" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -26158,6 +26695,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q299" s="10" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -26238,6 +26776,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q300" s="10" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -26318,6 +26857,11 @@
           <t>Commanditaire Vennootschap</t>
         </is>
       </c>
+      <c r="Q301" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -26398,6 +26942,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q302" s="10" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -26478,6 +27023,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q303" s="10" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -26558,6 +27104,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q304" s="10" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -26638,6 +27185,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q305" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -26718,6 +27270,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q306" s="10" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -26798,6 +27351,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q307" s="10" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -26878,6 +27432,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q308" s="10" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -26958,6 +27513,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q309" s="10" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -27038,6 +27594,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q310" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -27118,6 +27679,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q311" s="10" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -27198,6 +27760,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q312" s="10" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -27278,6 +27841,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q313" s="10" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -27358,6 +27922,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q314" s="10" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -27438,6 +28003,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q315" s="10" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -27518,6 +28084,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q316" s="10" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -27598,6 +28165,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q317" s="10" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -27678,6 +28246,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q318" s="10" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -27758,6 +28327,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q319" s="10" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -27838,6 +28408,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q320" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -27918,6 +28493,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q321" s="10" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -27998,6 +28574,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q322" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -28078,6 +28659,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q323" s="10" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -28158,6 +28740,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q324" s="10" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -28238,6 +28821,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q325" s="10" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -28318,6 +28902,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q326" s="10" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -28398,6 +28983,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q327" s="10" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -28478,6 +29064,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q328" s="10" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -28558,6 +29145,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q329" s="10" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -28638,6 +29226,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q330" s="10" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -28718,6 +29307,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q331" s="10" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -28798,6 +29388,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q332" s="10" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -28878,6 +29469,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q333" s="10" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -28958,6 +29550,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q334" s="10" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -29038,6 +29631,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q335" s="10" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -29118,6 +29712,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q336" s="10" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -29198,6 +29793,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q337" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -29278,6 +29878,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q338" s="10" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -29358,6 +29959,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q339" s="10" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -29438,6 +30040,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q340" s="10" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -29518,6 +30121,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q341" s="10" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -29598,6 +30202,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q342" s="10" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -29678,6 +30283,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q343" s="10" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -29758,6 +30364,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q344" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -29838,6 +30449,7 @@
           <t>Commanditaire Vennootschap met één beherende vennoot</t>
         </is>
       </c>
+      <c r="Q345" s="10" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -29918,6 +30530,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q346" s="10" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -29994,6 +30607,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q347" s="10" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -30074,6 +30688,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q348" s="10" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -30154,6 +30769,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q349" s="10" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -30234,6 +30850,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q350" s="10" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -30314,6 +30931,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q351" s="10" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -30394,6 +31012,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q352" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -30474,6 +31097,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q353" s="10" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -30554,6 +31178,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q354" s="10" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -30634,6 +31259,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q355" s="10" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -30714,6 +31340,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q356" s="10" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -30794,6 +31421,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q357" s="10" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -30874,6 +31502,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q358" s="10" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -30954,6 +31583,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q359" s="10" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -31034,6 +31664,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q360" s="10" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -31114,6 +31745,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q361" s="10" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -31194,6 +31826,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q362" s="10" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -31274,6 +31907,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q363" s="10" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -31354,6 +31988,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q364" s="10" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -31434,6 +32069,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q365" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -31514,6 +32154,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q366" s="10" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -31594,6 +32235,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q367" s="10" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -31674,6 +32316,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q368" s="10" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -31754,6 +32397,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q369" s="10" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -31834,6 +32478,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q370" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -31914,6 +32563,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q371" s="10" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -31994,6 +32644,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q372" s="10" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -32074,6 +32725,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q373" s="10" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -32154,6 +32806,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q374" s="10" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -32234,6 +32887,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q375" s="10" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -32314,6 +32968,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q376" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -32394,6 +33053,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q377" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -32474,6 +33138,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q378" s="10" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -32554,6 +33219,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q379" s="10" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -32634,6 +33300,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q380" s="10" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -32714,6 +33381,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q381" s="10" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -32794,6 +33462,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q382" s="10" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -32874,6 +33543,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q383" s="10" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -32954,6 +33624,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q384" s="10" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -33034,6 +33705,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q385" s="10" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -33114,6 +33786,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q386" s="10" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -33194,6 +33867,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q387" s="10" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -33274,6 +33948,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q388" s="10" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -33354,6 +34029,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q389" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -33434,6 +34114,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q390" s="10" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -33514,6 +34195,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q391" s="10" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -33594,6 +34276,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q392" s="10" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -33674,6 +34357,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q393" s="10" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -33754,6 +34438,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q394" s="10" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -33830,6 +34515,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q395" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -33910,6 +34600,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q396" s="10" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -33990,6 +34681,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q397" s="10" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -34070,6 +34762,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q398" s="10" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -34150,6 +34843,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q399" s="10" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -34230,6 +34924,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q400" s="10" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -34310,6 +35005,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q401" s="10" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -34390,6 +35086,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q402" s="10" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -34470,6 +35167,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q403" s="10" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -34550,6 +35248,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q404" s="10" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -34630,6 +35329,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q405" s="10" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -34710,6 +35410,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q406" s="10" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -34786,6 +35487,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q407" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -34866,6 +35572,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q408" s="10" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -34946,6 +35653,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q409" s="10" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -35026,6 +35734,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q410" s="10" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -35106,6 +35815,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q411" s="10" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -35186,6 +35896,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q412" s="10" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -35266,6 +35977,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q413" s="10" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -35346,6 +36058,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q414" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -35426,6 +36143,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q415" s="10" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -35506,6 +36224,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q416" s="10" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -35586,6 +36305,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q417" s="10" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -35666,6 +36386,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q418" s="10" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -35746,6 +36467,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q419" s="10" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -35826,6 +36548,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q420" s="10" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -35906,6 +36629,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q421" s="10" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -35986,6 +36710,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q422" s="10" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -36066,6 +36791,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q423" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -36146,6 +36876,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q424" s="10" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -36226,6 +36957,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q425" s="10" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -36306,6 +37038,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q426" s="10" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -36386,6 +37119,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q427" s="10" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -36466,6 +37200,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q428" s="10" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -36546,6 +37281,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q429" s="10" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -36598,6 +37334,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q430" s="10" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -36676,6 +37413,11 @@
       <c r="P431" t="inlineStr">
         <is>
           <t>Besloten vennootschap met gewone structuur</t>
+        </is>
+      </c>
+      <c r="Q431" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -36730,6 +37472,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q432" s="10" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -36810,6 +37553,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q433" s="10" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -36890,6 +37634,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q434" s="10" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -36970,6 +37715,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q435" s="10" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -37050,6 +37796,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q436" s="10" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -37130,6 +37877,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q437" s="10" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -37206,6 +37954,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q438" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -37286,6 +38039,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q439" s="10" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -37366,6 +38120,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q440" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -37446,6 +38205,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q441" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -37526,6 +38290,7 @@
           <t>Buitenlandse EG-vennootschap met onderneming in Nederland</t>
         </is>
       </c>
+      <c r="Q442" s="10" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -37606,6 +38371,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q443" s="10" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -37686,6 +38452,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q444" s="10" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -37766,6 +38533,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q445" s="10" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -37846,6 +38614,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q446" s="10" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -37926,6 +38695,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q447" s="10" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -38006,6 +38776,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q448" s="10" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -38086,6 +38857,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q449" s="10" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -38166,6 +38938,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q450" s="10" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -38246,6 +39019,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q451" s="10" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -38326,6 +39100,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q452" s="10" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -38406,6 +39181,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q453" s="10" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -38486,6 +39262,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q454" s="10" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -38566,6 +39343,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q455" s="10" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -38646,6 +39424,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q456" s="10" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -38726,6 +39505,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q457" s="10" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -38806,6 +39586,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q458" s="10" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -38886,6 +39667,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q459" s="10" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -38966,6 +39748,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q460" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -39046,6 +39833,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q461" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -39126,6 +39918,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q462" s="10" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -39206,6 +39999,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q463" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -39286,6 +40084,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q464" s="10" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -39366,6 +40165,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q465" s="10" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -39446,6 +40246,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q466" s="10" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -39526,6 +40327,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q467" s="10" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -39606,6 +40408,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q468" s="10" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -39686,6 +40489,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q469" s="10" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -39766,6 +40570,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q470" s="10" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -39818,6 +40623,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q471" s="10" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -39898,6 +40704,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q472" s="10" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -39978,6 +40785,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q473" s="10" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -40058,6 +40866,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q474" s="10" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -40138,6 +40947,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q475" s="10" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -40218,6 +41028,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q476" s="10" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -40298,6 +41109,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q477" s="10" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -40378,6 +41190,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q478" s="10" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -40458,6 +41271,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q479" s="10" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -40538,6 +41352,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q480" s="10" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -40618,6 +41433,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q481" s="10" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -40698,6 +41514,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q482" s="10" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -40778,6 +41595,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q483" s="10" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -40858,6 +41676,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q484" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -40938,6 +41761,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q485" s="10" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -41018,6 +41842,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q486" s="10" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -41098,6 +41923,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q487" s="10" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -41178,6 +42004,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q488" s="10" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -41258,6 +42085,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q489" s="10" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -41338,6 +42166,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q490" s="10" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -41418,6 +42247,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q491" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -41498,6 +42332,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q492" s="10" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -41578,6 +42413,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q493" s="10" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -41658,6 +42494,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q494" s="10" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -41738,6 +42575,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q495" s="10" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -41818,6 +42656,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q496" s="10" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -41898,6 +42737,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q497" s="10" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -41978,6 +42818,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q498" s="10" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -42058,6 +42899,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q499" s="10" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -42138,6 +42980,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q500" s="10" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -42218,6 +43061,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q501" s="10" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -42298,6 +43142,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q502" s="10" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -42378,6 +43223,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q503" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -42458,6 +43308,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q504" s="10" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -42538,6 +43389,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q505" s="10" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -42618,6 +43470,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q506" s="10" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -42698,6 +43551,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q507" s="10" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -42778,6 +43632,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q508" s="10" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -42858,6 +43713,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q509" s="10" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -42938,6 +43794,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q510" s="10" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -43018,6 +43875,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q511" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -43098,6 +43960,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q512" s="10" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -43178,6 +44041,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q513" s="10" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -43258,6 +44122,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q514" s="10" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -43338,6 +44203,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q515" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -43418,6 +44288,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q516" s="10" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -43498,6 +44369,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q517" s="10" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -43578,6 +44450,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q518" s="10" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -43658,6 +44531,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q519" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -43738,6 +44616,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q520" s="10" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -43818,6 +44697,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q521" s="10" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -43898,6 +44778,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q522" s="10" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -43978,6 +44859,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q523" s="10" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -44050,6 +44932,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q524" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -44130,6 +45017,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q525" s="10" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -44210,6 +45098,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q526" s="10" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -44290,6 +45179,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q527" s="10" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -44370,6 +45260,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q528" s="10" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -44450,6 +45341,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q529" s="10" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -44530,6 +45422,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q530" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -44610,6 +45507,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q531" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -44690,6 +45592,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q532" s="10" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -44770,6 +45673,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q533" s="10" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -44850,6 +45754,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q534" s="10" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -44930,6 +45835,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q535" s="10" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -45010,6 +45916,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q536" s="10" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -45090,6 +45997,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q537" s="10" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -45166,6 +46074,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q538" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -45246,6 +46159,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q539" s="10" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -45326,6 +46240,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q540" s="10" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -45406,6 +46321,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q541" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -45486,6 +46406,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q542" s="10" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -45566,6 +46487,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q543" s="10" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -45646,6 +46568,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q544" s="10" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -45726,6 +46649,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q545" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -45806,6 +46734,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q546" s="10" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -45886,6 +46815,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q547" s="10" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -45966,6 +46896,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q548" s="10" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -46046,6 +46977,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q549" s="10" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -46126,6 +47058,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q550" s="10" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -46206,6 +47139,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q551" s="10" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -46286,6 +47220,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q552" s="10" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -46366,6 +47301,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q553" s="10" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -46446,6 +47382,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q554" s="10" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -46526,6 +47463,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q555" s="10" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -46606,6 +47544,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q556" s="10" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -46686,6 +47625,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q557" s="10" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -46766,6 +47706,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q558" s="10" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -46846,6 +47787,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q559" s="10" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -46926,6 +47868,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q560" s="10" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -47006,6 +47949,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q561" s="10" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -47086,6 +48030,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q562" s="10" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -47166,6 +48111,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q563" s="10" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -47246,6 +48192,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q564" s="10" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -47326,6 +48273,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q565" s="10" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -47406,6 +48354,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q566" s="10" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -47486,6 +48435,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q567" s="10" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -47566,6 +48516,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q568" s="10" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -47646,6 +48597,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q569" s="10" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -47726,6 +48678,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q570" s="10" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -47806,6 +48759,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q571" s="10" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -47886,6 +48840,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q572" s="10" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -47966,6 +48921,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q573" s="10" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -48046,6 +49002,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q574" s="10" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -48126,6 +49083,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q575" s="10" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -48206,6 +49164,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q576" s="10" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -48286,6 +49245,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q577" s="10" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -48366,6 +49326,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q578" s="10" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -48446,6 +49407,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q579" s="10" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -48526,6 +49488,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q580" s="10" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -48606,6 +49569,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q581" s="10" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -48686,6 +49650,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q582" s="10" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -48766,6 +49731,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q583" s="10" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -48846,6 +49812,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q584" s="10" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -48926,6 +49893,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q585" s="10" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -49006,6 +49974,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q586" s="10" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -49086,6 +50055,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q587" s="10" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -49166,6 +50136,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q588" s="10" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -49246,6 +50217,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q589" s="10" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -49322,6 +50294,11 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q590" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -49402,6 +50379,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q591" s="10" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -49482,6 +50460,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q592" s="10" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -49562,6 +50541,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q593" s="10" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -49642,6 +50622,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q594" s="10" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -49722,6 +50703,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q595" s="10" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -49802,6 +50784,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q596" s="10" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -49882,6 +50865,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q597" s="10" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -49962,6 +50946,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q598" s="10" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -50042,6 +51027,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q599" s="10" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -50122,6 +51108,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q600" s="10" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -50202,6 +51189,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q601" s="10" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -50282,6 +51270,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q602" s="10" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -50362,6 +51351,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q603" s="10" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -50442,6 +51432,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q604" s="10" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -50522,6 +51513,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q605" s="10" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -50602,6 +51594,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q606" s="10" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -50682,6 +51675,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q607" s="10" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -50762,6 +51756,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q608" s="10" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -50842,6 +51837,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q609" s="10" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -50922,6 +51918,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q610" s="10" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -51002,6 +51999,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q611" s="10" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -51082,6 +52080,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q612" s="10" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -51162,6 +52161,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q613" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -51242,6 +52246,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q614" s="10" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -51322,6 +52327,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q615" s="10" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -51402,6 +52408,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q616" s="10" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -51482,6 +52489,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q617" s="10" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -51562,6 +52570,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q618" s="10" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -51642,6 +52651,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q619" s="10" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -51722,6 +52732,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q620" s="10" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -51802,6 +52813,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q621" s="10" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -51882,6 +52894,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q622" s="10" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -51962,6 +52975,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q623" s="10" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -52042,6 +53056,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q624" s="10" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -52122,6 +53137,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q625" s="10" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -52202,6 +53218,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q626" s="10" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -52282,6 +53299,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q627" s="10" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -52362,6 +53380,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q628" s="10" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -52442,6 +53461,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q629" s="10" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -52522,6 +53542,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q630" s="10" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -52602,6 +53623,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q631" s="10" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -52682,6 +53704,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q632" s="10" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -52762,6 +53785,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q633" s="10" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -52842,6 +53866,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q634" s="10" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -52922,6 +53947,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q635" s="10" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -53002,6 +54028,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q636" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -53082,6 +54113,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q637" s="10" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -53162,6 +54194,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q638" s="10" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -53242,6 +54275,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q639" s="10" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -53322,6 +54356,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q640" s="10" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -53402,6 +54437,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q641" s="10" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -53482,6 +54518,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q642" s="10" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -53562,6 +54599,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q643" s="10" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -53642,6 +54680,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q644" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -53722,6 +54765,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q645" s="10" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -53802,6 +54846,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q646" s="10" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -53882,6 +54927,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q647" s="10" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -53958,6 +55004,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q648" s="10" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -54038,6 +55085,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q649" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -54118,6 +55170,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q650" s="10" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -54198,6 +55251,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q651" s="10" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -54278,6 +55332,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q652" s="10" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -54358,6 +55413,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q653" s="10" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -54438,6 +55494,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q654" s="10" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -54518,6 +55575,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q655" s="10" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -54598,6 +55656,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q656" s="10" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -54678,6 +55737,11 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q657" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -54758,6 +55822,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q658" s="10" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -54838,6 +55903,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q659" s="10" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -54918,6 +55984,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q660" s="10" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -54998,6 +56065,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q661" s="10" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -55078,6 +56146,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q662" s="10" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -55158,6 +56227,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q663" s="10" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -55238,6 +56308,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q664" s="10" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -55318,6 +56389,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q665" s="10" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -55398,6 +56470,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q666" s="10" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -55478,6 +56551,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q667" s="10" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -55558,6 +56632,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q668" s="10" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -55638,6 +56713,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q669" s="10" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -55718,6 +56794,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q670" s="10" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -55798,6 +56875,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q671" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -55878,6 +56960,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q672" s="10" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -55958,6 +57041,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q673" s="10" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -56038,6 +57122,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q674" s="10" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -56118,6 +57203,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q675" s="10" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -56198,6 +57284,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q676" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -56278,6 +57369,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q677" s="10" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -56358,6 +57450,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q678" s="10" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -56438,6 +57531,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q679" s="10" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -56518,6 +57612,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q680" s="10" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -56598,6 +57693,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q681" s="10" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -56678,6 +57774,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q682" s="10" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -56758,6 +57855,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q683" s="10" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -56838,6 +57936,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q684" s="10" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -56918,6 +58017,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q685" s="10" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -56998,6 +58098,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q686" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -57078,6 +58183,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q687" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -57158,6 +58268,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q688" s="10" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -57238,6 +58349,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q689" s="10" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -57318,6 +58430,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q690" s="10" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -57398,6 +58511,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q691" s="10" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -57478,6 +58592,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q692" s="10" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -57558,6 +58673,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q693" s="10" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -57638,6 +58754,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q694" s="10" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -57718,6 +58835,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q695" s="10" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -57798,6 +58916,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q696" s="10" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -57878,6 +58997,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q697" s="10" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -57958,6 +59078,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q698" s="10" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -58038,6 +59159,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q699" s="10" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -58118,6 +59240,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q700" s="10" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -58198,6 +59321,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q701" s="10" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -58278,6 +59402,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q702" s="10" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -58358,6 +59483,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q703" s="10" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -58438,6 +59564,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q704" s="10" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -58514,6 +59641,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q705" s="10" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -58594,6 +59722,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q706" s="10" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -58674,6 +59803,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q707" s="10" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -58754,6 +59884,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q708" s="10" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -58834,6 +59965,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q709" s="10" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -58914,6 +60046,7 @@
           <t>Besloten vennootschap met</t>
         </is>
       </c>
+      <c r="Q710" s="10" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -58994,6 +60127,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q711" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -59074,6 +60212,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q712" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -59154,6 +60297,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q713" s="10" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -59234,6 +60378,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q714" s="10" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -59314,6 +60459,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q715" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -59394,6 +60544,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q716" s="10" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -59474,6 +60625,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q717" s="10" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -59554,6 +60706,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q718" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -59634,6 +60791,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q719" s="10" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -59714,6 +60872,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q720" s="10" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -59794,6 +60953,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q721" s="10" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -59874,6 +61034,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q722" s="10" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -59954,6 +61115,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q723" s="10" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -60034,6 +61196,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q724" s="10" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -60114,6 +61277,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q725" s="10" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -60194,6 +61358,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q726" s="10" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -60274,6 +61439,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q727" s="10" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -60354,6 +61520,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q728" s="10" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -60434,6 +61601,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q729" s="10" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -60514,6 +61682,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q730" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -60594,6 +61767,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q731" s="10" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -60674,6 +61848,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q732" s="10" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -60754,6 +61929,11 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q733" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -60834,6 +62014,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q734" s="10" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -60914,6 +62095,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q735" s="10" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -60994,6 +62176,11 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q736" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -61074,6 +62261,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q737" s="10" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -61154,6 +62342,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q738" s="10" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -61234,6 +62423,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q739" s="10" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -61314,6 +62504,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q740" s="10" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -61394,6 +62585,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q741" s="10" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -61474,6 +62666,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q742" s="10" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -61554,6 +62747,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q743" s="10" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -61634,6 +62828,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q744" s="10" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -61714,6 +62909,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q745" s="10" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -61794,6 +62990,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q746" s="10" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -61874,6 +63071,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q747" s="10" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -61954,6 +63152,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q748" s="10" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -62034,6 +63233,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q749" s="10" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -62114,6 +63314,7 @@
           <t>Onbekend</t>
         </is>
       </c>
+      <c r="Q750" s="10" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -62194,6 +63395,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q751" s="10" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -62274,6 +63476,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q752" s="10" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -62354,6 +63557,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q753" s="10" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -62434,6 +63638,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q754" s="10" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -62514,6 +63719,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q755" s="10" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -62594,6 +63800,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q756" s="10" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -62674,6 +63881,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q757" s="10" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -62754,6 +63962,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q758" s="10" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -62834,6 +64043,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q759" s="10" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -62914,6 +64124,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q760" s="10" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -62994,6 +64205,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q761" s="10" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -63074,6 +64286,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q762" s="10" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -63154,6 +64367,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q763" s="10" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -63234,6 +64448,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q764" s="10" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -63314,6 +64529,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q765" s="10" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -63394,6 +64610,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q766" s="10" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -63474,6 +64691,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q767" s="10" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -63554,6 +64772,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q768" s="10" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -63634,6 +64853,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q769" s="10" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -63714,6 +64934,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q770" s="10" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -63794,6 +65015,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q771" s="10" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -63874,6 +65096,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q772" s="10" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -63954,6 +65177,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q773" s="10" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -64034,6 +65258,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q774" s="10" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -64114,6 +65339,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q775" s="10" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -64194,6 +65420,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q776" s="10" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -64274,6 +65501,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q777" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -64354,6 +65586,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q778" s="10" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -64434,6 +65667,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q779" s="10" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -64514,6 +65748,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q780" s="10" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -64594,6 +65829,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q781" s="10" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -64674,6 +65910,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q782" s="10" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -64754,6 +65991,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q783" s="10" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -64834,6 +66072,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q784" s="10" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -64914,6 +66153,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q785" s="10" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -64994,6 +66234,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q786" s="10" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -65074,6 +66315,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q787" s="10" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -65154,6 +66396,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q788" s="10" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -65234,6 +66477,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q789" s="10" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -65314,6 +66558,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q790" s="10" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -65394,6 +66639,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q791" s="10" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -65474,6 +66720,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q792" s="10" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -65554,6 +66801,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q793" s="10" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -65634,6 +66882,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q794" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -65714,6 +66967,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q795" s="10" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -65794,6 +67048,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q796" s="10" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -65874,6 +67129,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q797" s="10" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -65954,6 +67210,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q798" s="10" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -66034,6 +67291,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q799" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -66114,6 +67376,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q800" s="10" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -66194,6 +67457,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q801" s="10" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -66274,6 +67538,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q802" s="10" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -66354,6 +67619,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q803" s="10" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -66434,6 +67700,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q804" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -66514,6 +67785,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q805" s="10" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -66594,6 +67866,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q806" s="10" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -66674,6 +67947,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q807" s="10" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -66754,6 +68028,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q808" s="10" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -66834,6 +68109,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q809" s="10" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -66914,6 +68190,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q810" s="10" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -66994,6 +68271,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q811" s="10" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -67074,6 +68352,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q812" s="10" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -67154,6 +68433,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q813" s="10" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -67234,6 +68514,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q814" s="10" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -67314,6 +68595,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q815" s="10" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -67394,6 +68676,11 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q816" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -67474,6 +68761,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q817" s="10" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -67554,6 +68842,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q818" s="10" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -67634,6 +68923,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q819" s="10" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -67714,6 +69004,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q820" s="10" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -67794,6 +69085,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q821" s="10" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -67874,6 +69166,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q822" s="10" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -67954,6 +69247,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q823" s="10" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -68034,6 +69328,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q824" s="10" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -68114,6 +69409,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q825" s="10" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -68194,6 +69490,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q826" s="10" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -68274,6 +69571,7 @@
           <t>Commanditaire vennootschap</t>
         </is>
       </c>
+      <c r="Q827" s="10" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -68354,6 +69652,7 @@
           <t>Commanditaire vennootschap</t>
         </is>
       </c>
+      <c r="Q828" s="10" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -68434,6 +69733,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q829" s="10" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -68514,6 +69814,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q830" s="10" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -68594,6 +69895,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q831" s="10" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -68674,6 +69976,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q832" s="10" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -68754,6 +70057,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q833" s="10" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -68834,6 +70138,7 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q834" s="10" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -68914,6 +70219,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q835" s="10" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -68994,6 +70300,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q836" s="10" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -69074,6 +70381,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q837" s="10" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -69154,6 +70462,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q838" s="10" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -69234,6 +70543,11 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q839" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -69314,6 +70628,11 @@
           <t>Vennootschap onder firma</t>
         </is>
       </c>
+      <c r="Q840" s="9" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -69394,6 +70713,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q841" s="10" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -69474,6 +70794,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q842" s="10" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -69554,6 +70875,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q843" s="10" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -69634,6 +70956,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q844" s="10" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -69714,6 +71037,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q845" s="10" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -69794,6 +71118,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q846" s="10" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -69874,6 +71199,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q847" s="10" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -69954,6 +71280,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q848" s="10" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -70034,6 +71361,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q849" s="10" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -70114,6 +71442,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q850" s="10" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -70194,6 +71523,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q851" s="10" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -70274,6 +71604,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q852" s="10" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -70354,6 +71685,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q853" s="10" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -70434,6 +71766,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q854" s="10" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -70514,6 +71847,7 @@
           <t>Besloten vennootschap met gewone structuur</t>
         </is>
       </c>
+      <c r="Q855" s="10" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -70594,6 +71928,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q856" s="10" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -70674,6 +72009,7 @@
           <t>Vennootschap Onder Firma</t>
         </is>
       </c>
+      <c r="Q857" s="10" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -70754,6 +72090,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q858" s="10" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -70834,6 +72171,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q859" s="10" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -70914,6 +72252,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q860" s="10" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -70994,6 +72333,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q861" s="10" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -71074,6 +72414,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q862" s="10" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -71154,6 +72495,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q863" s="10" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -71234,6 +72576,7 @@
           <t>Besloten Vennootschap</t>
         </is>
       </c>
+      <c r="Q864" s="10" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -71314,6 +72657,7 @@
           <t>Eenmanszaak</t>
         </is>
       </c>
+      <c r="Q865" s="10" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -71394,6 +72738,7 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q866" s="10" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -71474,9 +72819,10 @@
           <t>Besloten vennootschap</t>
         </is>
       </c>
+      <c r="Q867" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P867"/>
+  <autoFilter ref="A1:Q867"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -72428,7 +73774,7 @@
       <c r="C6" t="n">
         <v>253</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="11">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -72443,7 +73789,7 @@
       <c r="C7" t="n">
         <v>242</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -72458,7 +73804,7 @@
       <c r="C8" t="n">
         <v>199</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="11">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -72473,7 +73819,7 @@
       <c r="C9" t="n">
         <v>285</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="11">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -72488,7 +73834,7 @@
       <c r="C10" t="n">
         <v>253</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="11">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -72503,7 +73849,7 @@
       <c r="C11" t="n">
         <v>215</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="11">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -72518,7 +73864,7 @@
       <c r="C12" t="n">
         <v>164</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="11">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -72533,7 +73879,7 @@
       <c r="C13" t="n">
         <v>118</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="11">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -72548,7 +73894,7 @@
       <c r="C14" t="n">
         <v>119</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="11">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -72563,7 +73909,7 @@
       <c r="C15" t="n">
         <v>117</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="11">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -72578,7 +73924,7 @@
       <c r="C16" t="n">
         <v>122</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="11">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -72593,7 +73939,7 @@
       <c r="C17" t="n">
         <v>134</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="11">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -72608,7 +73954,7 @@
       <c r="C18" t="n">
         <v>77</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="11">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -72623,7 +73969,7 @@
       <c r="C19" t="n">
         <v>82</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="11">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -72638,7 +73984,7 @@
       <c r="C20" t="n">
         <v>137</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="11">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -72653,7 +73999,7 @@
       <c r="C21" t="n">
         <v>185</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="11">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -72668,7 +74014,7 @@
       <c r="C22" t="n">
         <v>142</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="11">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
